--- a/spreadsheet/SIMS-Blog-Manager-template-Product5.1-Official-Lean.xlsx
+++ b/spreadsheet/SIMS-Blog-Manager-template-Product5.1-Official-Lean.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="R788935f14c444e8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="Rf69c9174389041f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="Re6f6cbd051ca4ee8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="Rec88462187ca4d5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="R3192e532952d437d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="R185d08809315454a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="R1a586716bd3040b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="Ra0eef5d97e9345c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="R9d83bfc666b2425c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="Rc08eb4ad80bc4b43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="Rcf57ea8a41bc43f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="R73f71b38e5964a5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="R8c12c91aa0c34731"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="Rb218529738974dc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="R1c3e9ab51055444e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="R92d3f9a763554438"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="R43429f4a8a054f44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="R9c97468ab63344ca"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -345,7 +345,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="34" t="str">
-        <x:v>SIMS-Blog-Manager Product 5.1 Official</x:v>
+        <x:v>SIMS-Blog-Manager Product 5.1.1</x:v>
       </x:c>
       <x:c r="B1" s="35"/>
       <x:c r="C1" s="35"/>
@@ -5313,7 +5313,7 @@
         <x:v>Product Version</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>5.1 Official</x:v>
+        <x:v>5.1.1</x:v>
       </x:c>
       <x:c r="C2" t="str">
         <x:v>UI/UX改訂版。既存データ互換。</x:v>

--- a/spreadsheet/SIMS-Blog-Manager-template-Product5.1-Official-Lean.xlsx
+++ b/spreadsheet/SIMS-Blog-Manager-template-Product5.1-Official-Lean.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="Rc08eb4ad80bc4b43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="Rcf57ea8a41bc43f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="R73f71b38e5964a5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="R8c12c91aa0c34731"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="Rb218529738974dc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="R1c3e9ab51055444e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="R92d3f9a763554438"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="R43429f4a8a054f44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="R9c97468ab63344ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="Re8a7c3bf58464e56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R69bd4326e69e4db8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="R1614855c39a34422"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="R17b82003a2db4911"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="R16972ae55f4e4dbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="Rbef8753efdc64052"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="R9eead891998649ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="Rd75dd752e61e41fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="R785365055ad44d70"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -345,7 +345,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="34" t="str">
-        <x:v>SIMS-Blog-Manager Product 5.1.1</x:v>
+        <x:v>SIMS-Blog-Manager Product 5.1.2</x:v>
       </x:c>
       <x:c r="B1" s="35"/>
       <x:c r="C1" s="35"/>
@@ -5313,7 +5313,7 @@
         <x:v>Product Version</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>5.1.1</x:v>
+        <x:v>5.1.2</x:v>
       </x:c>
       <x:c r="C2" t="str">
         <x:v>UI/UX改訂版。既存データ互換。</x:v>

--- a/spreadsheet/SIMS-Blog-Manager-template-Product5.1-Official-Lean.xlsx
+++ b/spreadsheet/SIMS-Blog-Manager-template-Product5.1-Official-Lean.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="Re8a7c3bf58464e56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R69bd4326e69e4db8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="R1614855c39a34422"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="R17b82003a2db4911"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="R16972ae55f4e4dbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="Rbef8753efdc64052"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="R9eead891998649ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="Rd75dd752e61e41fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="R785365055ad44d70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="R76ddefe1f18e44ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="Rc289b98c945a4708"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="Ra2089efe56f84a04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="R4b4e63aa7d2e4a07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="R3ffc78c321eb424f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="R4249c3561ed6480e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="R9b0ee13c150449cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="R152da2d167414964"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="R84013bad24ec4548"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -345,7 +345,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="34" t="str">
-        <x:v>SIMS-Blog-Manager Product 5.1.2</x:v>
+        <x:v>SIMS-Blog-Manager Product 5.1.3</x:v>
       </x:c>
       <x:c r="B1" s="35"/>
       <x:c r="C1" s="35"/>
@@ -5313,7 +5313,7 @@
         <x:v>Product Version</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>5.1.2</x:v>
+        <x:v>5.1.3</x:v>
       </x:c>
       <x:c r="C2" t="str">
         <x:v>UI/UX改訂版。既存データ互換。</x:v>
